--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131975073</v>
+        <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>92327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hyggeskant väster Mattjärn, Mattjärn, Lindome, Hl</t>
+          <t>Hyggeskant väster Mattjärn, Hyggeskant väster Mattjärn, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334984</v>
+        <v>334663</v>
       </c>
       <c r="R2" t="n">
-        <v>6386768</v>
+        <v>6386702</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +748,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Currydoftande, kryddigt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +777,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,19 +789,19 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Mats Foss, Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131975073</t>
+          <t>https://artportalen.se/Sighting/136920062</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132886088</v>
+        <v>131975073</v>
       </c>
       <c r="B3" t="n">
         <v>57162</v>
@@ -820,34 +829,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hyggeskant väster Mattjärn, Mattjärn, Lindome, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334692</v>
+        <v>334984</v>
       </c>
       <c r="R3" t="n">
-        <v>6386660</v>
+        <v>6386768</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,11 +893,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -916,6 +906,137 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131975073</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132886088</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hyggeskant väster Mattjärn, Mattjärn, Lindome, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>334692</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6386660</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132886088</t>
         </is>
@@ -925,6 +1046,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92329</v>
+        <v>92331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48265-2025 artfynd.xlsx
+++ b/artfynd/A 48265-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920062</v>
       </c>
       <c r="B2" t="n">
-        <v>92400</v>
+        <v>92403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
